--- a/checklists/excel/self/readability.xlsx
+++ b/checklists/excel/self/readability.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Readability" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Readability Review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,116 +425,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Code is well-commented and self-documenting (GOOD)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Readability Review</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Complex logic explained; Function purposes documented; Business rules clarified</t>
+          <t>Verify code is well-commented and self-documenting</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Ensure complex logic is explained, function purposes are documented, and business rules are clarified for future maintainers.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Code should be easy to understand for future maintainers</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Code review and documentation analysis</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Variable and function names are descriptive (MUST)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Readability Review</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Names reflect purpose; No abbreviations; Consistent naming conventions</t>
+          <t>Check variable and function names are descriptive</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Ensure all variable and function names reflect their purpose, avoid abbreviations, and follow consistent naming conventions.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>All identifiers should clearly indicate their purpose</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Code review and static analysis tools</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Functions are focused and not too long (GOOD)</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Readability Review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Single responsibility principle; Reasonable length; Clear input/output</t>
+          <t>Verify functions are focused and not too long</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ensure functions follow single responsibility principle, have reasonable length, and have clear input/output.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Functions should be focused on a single task</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Code metrics analysis and review</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Code formatting follows project standards (MUST)</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Readability Review</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consistent indentation; Proper spacing; Line length limits respected</t>
+          <t>Check code formatting follows project standards</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ensure consistent indentation, proper spacing, and line length limits are respected according to project standards.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Code should be consistently formatted according to project standards</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Run formatter and check for violations</t>
         </is>
       </c>
     </row>
